--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124127035</v>
+        <v>124127261</v>
       </c>
       <c r="B2" t="n">
-        <v>57382</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321417</v>
+        <v>321416</v>
       </c>
       <c r="R2" t="n">
-        <v>6470038</v>
+        <v>6469840</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
+          <t>Ljudbox</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124127261</v>
+        <v>124127035</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57382</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321416</v>
+        <v>321417</v>
       </c>
       <c r="R4" t="n">
-        <v>6469840</v>
+        <v>6470038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ljudbox</t>
+          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124126887</v>
+        <v>124127035</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57404</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321347</v>
+        <v>321417</v>
       </c>
       <c r="R3" t="n">
-        <v>6469834</v>
+        <v>6470038</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +882,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124127035</v>
+        <v>124126887</v>
       </c>
       <c r="B4" t="n">
-        <v>57404</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -960,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321417</v>
+        <v>321347</v>
       </c>
       <c r="R4" t="n">
-        <v>6470038</v>
+        <v>6469834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,11 +1001,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124127261</v>
+        <v>124127035</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321416</v>
+        <v>321417</v>
       </c>
       <c r="R2" t="n">
-        <v>6469840</v>
+        <v>6470038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -767,7 +767,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Ljudbox</t>
+          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124127035</v>
+        <v>124127261</v>
       </c>
       <c r="B3" t="n">
-        <v>57404</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321417</v>
+        <v>321416</v>
       </c>
       <c r="R3" t="n">
-        <v>6470038</v>
+        <v>6469840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
+          <t>Ljudbox</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124127035</v>
+        <v>124126887</v>
       </c>
       <c r="B2" t="n">
-        <v>57404</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321417</v>
+        <v>321347</v>
       </c>
       <c r="R2" t="n">
-        <v>6470038</v>
+        <v>6469834</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -913,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124126887</v>
+        <v>124127035</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57404</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,21 +924,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321347</v>
+        <v>321417</v>
       </c>
       <c r="R4" t="n">
-        <v>6469834</v>
+        <v>6470038</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,6 +996,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124126887</v>
+        <v>124127035</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57404</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321347</v>
+        <v>321417</v>
       </c>
       <c r="R2" t="n">
-        <v>6469834</v>
+        <v>6470038</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124127261</v>
+        <v>124126887</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321416</v>
+        <v>321347</v>
       </c>
       <c r="R3" t="n">
-        <v>6469840</v>
+        <v>6469834</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,11 +882,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ljudbox</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124127035</v>
+        <v>124127261</v>
       </c>
       <c r="B4" t="n">
-        <v>57404</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100001</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321417</v>
+        <v>321416</v>
       </c>
       <c r="R4" t="n">
-        <v>6470038</v>
+        <v>6469840</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
+          <t>Ljudbox</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124126887</v>
+        <v>124127261</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321347</v>
+        <v>321416</v>
       </c>
       <c r="R3" t="n">
-        <v>6469834</v>
+        <v>6469840</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,6 +882,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ljudbox</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124127261</v>
+        <v>124126887</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -960,10 +965,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321416</v>
+        <v>321347</v>
       </c>
       <c r="R4" t="n">
-        <v>6469840</v>
+        <v>6469834</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,11 +1001,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ljudbox</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124127035</v>
       </c>
       <c r="B2" t="n">
-        <v>57404</v>
+        <v>57557</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>124126887</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>124127035</v>
       </c>
       <c r="B2" t="n">
-        <v>57557</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -916,12 +911,7 @@
         <v>124126887</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>133192828</v>
       </c>
       <c r="B5" t="n">
-        <v>96358</v>
+        <v>96360</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>133192818</v>
       </c>
       <c r="B6" t="n">
-        <v>96718</v>
+        <v>96720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>133192828</v>
       </c>
       <c r="B5" t="n">
-        <v>96360</v>
+        <v>96368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>133192818</v>
       </c>
       <c r="B6" t="n">
-        <v>96720</v>
+        <v>96728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -1020,7 +1020,7 @@
         <v>133192828</v>
       </c>
       <c r="B5" t="n">
-        <v>96368</v>
+        <v>96396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>133192818</v>
       </c>
       <c r="B6" t="n">
-        <v>96728</v>
+        <v>96756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124127035</v>
+        <v>133192818</v>
       </c>
       <c r="B2" t="n">
-        <v>57572</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100001</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 62051-2024, Boh</t>
+          <t>Sydväst om Spelemansbacken, Tureborg, Uddevalla, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321417</v>
+        <v>321402</v>
       </c>
       <c r="R2" t="n">
-        <v>6470038</v>
+        <v>6469801</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,17 +744,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
+          <t>Tre kuddar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,83 +773,76 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helene Jacobson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helene Jacobson, Bo Eriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124127261</v>
+        <v>133192828</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 62051-2024, Boh</t>
+          <t>Sydväst om Spelemansbacken, Tureborg, Uddevalla, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>321416</v>
+        <v>321402</v>
       </c>
       <c r="R3" t="n">
-        <v>6469840</v>
+        <v>6469801</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,17 +866,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ljudbox</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,78 +890,76 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helene Jacobson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helene Jacobson, Bo Eriksson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124126887</v>
+        <v>133193086</v>
       </c>
       <c r="B4" t="n">
-        <v>57811</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 62051-2024, Boh</t>
+          <t>V om Spelemansbacken, Tureborg, Uddevalla, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>321347</v>
+        <v>321382</v>
       </c>
       <c r="R4" t="n">
-        <v>6469834</v>
+        <v>6469887</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +983,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,70 +1007,79 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helene Jacobson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Johansson</t>
+          <t>Helene Jacobson, Bo Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133192828</v>
+        <v>124127035</v>
       </c>
       <c r="B5" t="n">
-        <v>96396</v>
+        <v>57874</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>100001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sydväst om Spelemansbacken, Tureborg, Uddevalla, Boh</t>
+          <t>A 62051-2024, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>321402</v>
+        <v>321417</v>
       </c>
       <c r="R5" t="n">
-        <v>6469801</v>
+        <v>6470038</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,22 +1103,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Kretsade över avverkningsanmälan. Kontaktläte. Möjlig häckning i närheten</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,34 +1122,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Helene Jacobson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Jacobson, Bo Eriksson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133192818</v>
+        <v>124127261</v>
       </c>
       <c r="B6" t="n">
-        <v>96756</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,41 +1151,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sydväst om Spelemansbacken, Tureborg, Uddevalla, Boh</t>
+          <t>A 62051-2024, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>321402</v>
+        <v>321416</v>
       </c>
       <c r="R6" t="n">
-        <v>6469801</v>
+        <v>6469840</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,27 +1217,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Tre kuddar</t>
+          <t>Ljudbox</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,27 +1236,130 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Helene Jacobson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Helene Jacobson, Bo Eriksson</t>
+          <t>Christer Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124126887</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 62051-2024, Boh</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>321347</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6469834</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Christer Johansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Jacobson, Bo Eriksson</t>
+          <t>Bo Eriksson, Helene Jacobson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helene Jacobson, Bo Eriksson</t>
+          <t>Bo Eriksson, Helene Jacobson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bo Eriksson, Helene Jacobson</t>
+          <t>Helene Jacobson, Bo Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Eriksson, Helene Jacobson</t>
+          <t>Helene Jacobson, Bo Eriksson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -794,6 +799,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133192818</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133192828</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134987100</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1135,6 +1155,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133193086</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124127035</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1363,6 +1393,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124127261</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124126887</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1584,6 +1624,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134986988</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1696,6 +1741,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134986070</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1808,6 +1858,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134986090</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1920,6 +1975,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134987260</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134987113</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2144,6 +2209,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134985732</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2261,8 +2331,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134887155</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>134987100</v>
       </c>
       <c r="B4" t="n">
-        <v>96423</v>
+        <v>96467</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>134986988</v>
       </c>
       <c r="B9" t="n">
-        <v>106199</v>
+        <v>106254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>134986070</v>
       </c>
       <c r="B10" t="n">
-        <v>106358</v>
+        <v>106413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>134986090</v>
       </c>
       <c r="B11" t="n">
-        <v>107695</v>
+        <v>107750</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>134987260</v>
       </c>
       <c r="B12" t="n">
-        <v>99853</v>
+        <v>99900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>134987113</v>
       </c>
       <c r="B13" t="n">
-        <v>99504</v>
+        <v>99551</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>134985732</v>
       </c>
       <c r="B14" t="n">
-        <v>98249</v>
+        <v>98293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 62051-2024 artfynd.xlsx
+++ b/artfynd/A 62051-2024 artfynd.xlsx
@@ -932,7 +932,7 @@
         <v>134987100</v>
       </c>
       <c r="B4" t="n">
-        <v>96467</v>
+        <v>96494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>134986988</v>
       </c>
       <c r="B9" t="n">
-        <v>106254</v>
+        <v>106281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         <v>134986070</v>
       </c>
       <c r="B10" t="n">
-        <v>106413</v>
+        <v>106440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>134986090</v>
       </c>
       <c r="B11" t="n">
-        <v>107750</v>
+        <v>107777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
         <v>134987260</v>
       </c>
       <c r="B12" t="n">
-        <v>99900</v>
+        <v>99927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>134987113</v>
       </c>
       <c r="B13" t="n">
-        <v>99551</v>
+        <v>99578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>134985732</v>
       </c>
       <c r="B14" t="n">
-        <v>98293</v>
+        <v>98320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
